--- a/informes_data/Primera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_SÚPER AGROPAL PALENCIA.xlsx
+++ b/informes_data/Primera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_SÚPER AGROPAL PALENCIA.xlsx
@@ -565,13 +565,13 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>16.2729</v>
+        <v>13.5568</v>
       </c>
       <c r="E2" t="n">
-        <v>14.9488</v>
+        <v>12.7226</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3241</v>
+        <v>0.8341999999999996</v>
       </c>
       <c r="G2" t="n">
         <v>4.1715</v>
@@ -610,13 +610,13 @@
         <v>6.1677</v>
       </c>
       <c r="S2" t="n">
-        <v>6.137700000000001</v>
+        <v>3.421600000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>4.6766</v>
+        <v>2.4506</v>
       </c>
       <c r="U2" t="n">
-        <v>1.461</v>
+        <v>0.9708999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>5.5232</v>
@@ -643,13 +643,13 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>11.3211</v>
+        <v>10.5883</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9016</v>
+        <v>6.8487</v>
       </c>
       <c r="F3" t="n">
-        <v>4.419499999999999</v>
+        <v>3.7398</v>
       </c>
       <c r="G3" t="n">
         <v>6.994899999999999</v>
@@ -688,13 +688,13 @@
         <v>2.8636</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6389</v>
+        <v>2.9063</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9823999999999999</v>
+        <v>0.9292</v>
       </c>
       <c r="U3" t="n">
-        <v>2.6565</v>
+        <v>1.9768</v>
       </c>
       <c r="V3" t="n">
         <v>1.1279</v>
@@ -721,13 +721,13 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>7.2499</v>
+        <v>6.8539</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3498</v>
+        <v>3.8183</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9001</v>
+        <v>3.0354</v>
       </c>
       <c r="G4" t="n">
         <v>1.5811</v>
@@ -766,13 +766,13 @@
         <v>1.9824</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6028</v>
+        <v>2.2068</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3935</v>
+        <v>0.8621000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2093</v>
+        <v>1.3444</v>
       </c>
       <c r="V4" t="n">
         <v>1.3039</v>
@@ -799,13 +799,13 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>6.7364</v>
+        <v>6.2183</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7485000000000001</v>
+        <v>-0.6464000000000004</v>
       </c>
       <c r="F5" t="n">
-        <v>5.9878</v>
+        <v>6.864800000000001</v>
       </c>
       <c r="G5" t="n">
         <v>2.7254</v>
@@ -844,13 +844,13 @@
         <v>6.3879</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1472</v>
+        <v>1.6291</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5413</v>
+        <v>1.1463</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3941</v>
+        <v>0.4826</v>
       </c>
       <c r="V5" t="n">
         <v>4.5072</v>
@@ -877,13 +877,13 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6495</v>
+        <v>4.7355</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0397</v>
+        <v>2.5083</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6097</v>
+        <v>2.2273</v>
       </c>
       <c r="G6" t="n">
         <v>-1.1173</v>
@@ -922,13 +922,13 @@
         <v>4.846</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7680999999999999</v>
+        <v>1.8543</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3418</v>
+        <v>0.8105</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4264</v>
+        <v>1.0439</v>
       </c>
       <c r="V6" t="n">
         <v>1.5754</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MUÑOZ BORCHERS</t>
+          <t>T. BORG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2696</v>
+        <v>2.9065</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2696</v>
+        <v>0.8457999999999994</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2.0606</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2696</v>
+        <v>4.925</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2696</v>
+        <v>1.0561</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>3.8689</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2696</v>
+        <v>5.9023</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2696</v>
+        <v>1.2692</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4.6332</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-0.9773999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.2132000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.7642000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-3.3042</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-7.7095</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>4.4054</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.5366000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.9746</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.4379</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.7489000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.6784</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.9294</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. LEVY</t>
+          <t>A. MUÑOZ BORCHERS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4263</v>
+        <v>0.2696</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6348</v>
+        <v>0.2696</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2084</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3988</v>
+        <v>0.2696</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3899</v>
+        <v>0.2696</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0089</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2007</v>
+        <v>0.2696</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5931</v>
+        <v>0.2696</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6076</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1981</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2032</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4014</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.7622</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2027</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4405</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6224</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1922</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4302</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5595</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5595</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. BORG</t>
+          <t>G. LEVY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-0.3046</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0302</v>
+        <v>-0.5707</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1959</v>
+        <v>0.2661</v>
       </c>
       <c r="G9" t="n">
-        <v>4.925</v>
+        <v>1.3988</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0561</v>
+        <v>0.3899</v>
       </c>
       <c r="I9" t="n">
-        <v>3.8689</v>
+        <v>1.0089</v>
       </c>
       <c r="J9" t="n">
-        <v>5.9023</v>
+        <v>1.2007</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2692</v>
+        <v>0.5931</v>
       </c>
       <c r="L9" t="n">
-        <v>4.6332</v>
+        <v>0.6076</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9773999999999999</v>
+        <v>0.1981</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2132000000000001</v>
+        <v>-0.2032</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7642000000000001</v>
+        <v>0.4014</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.3042</v>
+        <v>-1.7622</v>
       </c>
       <c r="Q9" t="n">
-        <v>-7.7095</v>
+        <v>-2.2027</v>
       </c>
       <c r="R9" t="n">
-        <v>4.4054</v>
+        <v>0.4405</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.2041</v>
+        <v>-0.5007</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.9013</v>
+        <v>-0.1281</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.3027</v>
+        <v>-0.3726</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7489000000000001</v>
+        <v>0.5595</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6784</v>
+        <v>0.5595</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>M. RODRIGUEZ BARRIENTOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9613999999999998</v>
+        <v>-1.3306</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7431000000000001</v>
+        <v>-0.0452999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2182000000000002</v>
+        <v>-1.2854</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.4312</v>
+        <v>-0.2899</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.2992</v>
+        <v>-0.6816</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.132</v>
+        <v>0.3916999999999997</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2361</v>
+        <v>0.2328000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.945</v>
+        <v>0.1078</v>
       </c>
       <c r="L10" t="n">
-        <v>1.7088</v>
+        <v>0.125</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.1949</v>
+        <v>-0.5226999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3542000000000001</v>
+        <v>-0.7894000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.8408</v>
+        <v>0.2668</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>0.4405</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.3042</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.304</v>
+        <v>0.4405</v>
       </c>
       <c r="S10" t="n">
-        <v>4.301600000000001</v>
+        <v>-0.3625</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5505</v>
+        <v>-0.2781</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7509000000000001</v>
+        <v>-0.0843</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8318</v>
+        <v>-1.1189</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7534000000000001</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0783</v>
+        <v>-1.1189</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ BARRIENTOS</t>
+          <t>A. KUNKEL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8597</v>
+        <v>-2.333500000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3436000000000001</v>
+        <v>-3.1327</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5159</v>
+        <v>0.7989999999999997</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2899</v>
+        <v>-1.7455</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6816</v>
+        <v>2.0047</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3916999999999997</v>
+        <v>-3.7502</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2328000000000001</v>
+        <v>0.4298</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1078</v>
+        <v>2.3437</v>
       </c>
       <c r="L11" t="n">
-        <v>0.125</v>
+        <v>-1.914</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5226999999999999</v>
+        <v>-2.1752</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7894000000000001</v>
+        <v>-0.339</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2668</v>
+        <v>-1.8362</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4405</v>
+        <v>-4.4054</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-8.8108</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4405</v>
+        <v>4.4054</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8914</v>
+        <v>1.8402</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5765</v>
+        <v>0.7729</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.315</v>
+        <v>1.0674</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.1189</v>
+        <v>1.977</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>4.4756</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1189</v>
+        <v>-2.4986</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3921</v>
+        <v>-2.9246</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5939999999999999</v>
+        <v>-0.5298999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7982</v>
+        <v>-2.3946</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2124000000000001</v>
@@ -1390,13 +1390,13 @@
         <v>4.4055</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7781</v>
+        <v>1.2459</v>
       </c>
       <c r="T12" t="n">
-        <v>0.787</v>
+        <v>0.851</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.00880000000000003</v>
+        <v>0.3947999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>0.4476</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. KUNKEL</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8996</v>
+        <v>-3.0871</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.773</v>
+        <v>-2.4366</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8735000000000002</v>
+        <v>-0.6506000000000003</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.7455</v>
+        <v>-3.4312</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0047</v>
+        <v>-2.2992</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.7502</v>
+        <v>-1.132</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4298</v>
+        <v>-0.2361</v>
       </c>
       <c r="K13" t="n">
-        <v>2.3437</v>
+        <v>-1.945</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.914</v>
+        <v>1.7088</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.1752</v>
+        <v>-3.1949</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.339</v>
+        <v>-0.3542000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.8362</v>
+        <v>-2.8408</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.4054</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="Q13" t="n">
-        <v>-8.8108</v>
+        <v>-3.3042</v>
       </c>
       <c r="R13" t="n">
-        <v>4.4054</v>
+        <v>3.304</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2744</v>
+        <v>2.1758</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8674000000000001</v>
+        <v>1.8571</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1417</v>
+        <v>0.3186</v>
       </c>
       <c r="V13" t="n">
-        <v>1.977</v>
+        <v>-1.8318</v>
       </c>
       <c r="W13" t="n">
-        <v>4.4756</v>
+        <v>-0.7534000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.4986</v>
+        <v>-1.0783</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.468299999999999</v>
+        <v>-6.0687</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.1162</v>
+        <v>-5.988200000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3521000000000001</v>
+        <v>-0.08050000000000024</v>
       </c>
       <c r="G14" t="n">
         <v>-3.8159</v>
@@ -1546,13 +1546,13 @@
         <v>5.5067</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3703</v>
+        <v>1.77</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9151</v>
+        <v>1.0432</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4552</v>
+        <v>0.727</v>
       </c>
       <c r="V14" t="n">
         <v>-3.8025</v>
@@ -1579,13 +1579,13 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>27.65780000000001</v>
+        <v>29.07980000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>13.02310000000001</v>
+        <v>13.6635</v>
       </c>
       <c r="F15" t="n">
-        <v>14.6346</v>
+        <v>15.4161</v>
       </c>
       <c r="G15" t="n">
         <v>11.4541</v>
@@ -1594,13 +1594,13 @@
         <v>2.729900000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>8.723900000000002</v>
+        <v>8.7239</v>
       </c>
       <c r="J15" t="n">
         <v>32.8118</v>
       </c>
       <c r="K15" t="n">
-        <v>6.506900000000001</v>
+        <v>6.506900000000002</v>
       </c>
       <c r="L15" t="n">
         <v>26.3046</v>
@@ -1618,19 +1618,19 @@
         <v>-12.1152</v>
       </c>
       <c r="Q15" t="n">
-        <v>-57.27119999999999</v>
+        <v>-57.27120000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>45.1556</v>
+        <v>45.15560000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>17.3012</v>
+        <v>18.7234</v>
       </c>
       <c r="T15" t="n">
-        <v>10.6508</v>
+        <v>11.2913</v>
       </c>
       <c r="U15" t="n">
-        <v>6.6502</v>
+        <v>7.4316</v>
       </c>
       <c r="V15" t="n">
         <v>11.0174</v>
